--- a/sheets/personal-finance/roth-ira-conversion-ladder-planner/roth-ira-conversion-ladder-planner.xlsx
+++ b/sheets/personal-finance/roth-ira-conversion-ladder-planner/roth-ira-conversion-ladder-planner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\000_drive_drive\600_PROJECTS\modelstack\sheets\personal-finance\roth-ira-conversion-ladder-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ECCEE7-C1F2-4B73-BA41-8D4F646364D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E064A4-65A1-4CC3-8119-427F3473F03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="117">
   <si>
     <t>Year</t>
   </si>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>Cash / Savings</t>
-  </si>
-  <si>
-    <t>B16 caps rows on Conversion Schedule (max 35).</t>
   </si>
   <si>
     <t>Current Age</t>
@@ -940,13 +937,11 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="10">
         <v>48</v>
@@ -954,7 +949,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="10">
         <v>46</v>
@@ -962,15 +957,15 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="9">
         <v>32000</v>
@@ -978,7 +973,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="11">
         <v>0.05</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9">
         <v>65000</v>
@@ -994,7 +989,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="11">
         <v>0.06</v>
@@ -1002,7 +997,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="10">
         <v>15</v>
@@ -1010,7 +1005,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="12">
         <v>2025</v>
@@ -1018,7 +1013,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="12">
         <v>7</v>
@@ -1026,7 +1021,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" s="9">
         <v>50000</v>
@@ -1034,7 +1029,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="9">
         <v>55000</v>
@@ -1042,7 +1037,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="9">
         <v>60000</v>
@@ -1050,7 +1045,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="9">
         <v>62000</v>
@@ -1058,7 +1053,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="9">
         <v>65000</v>
@@ -1066,7 +1061,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="9">
         <v>68000</v>
@@ -1074,7 +1069,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="9">
         <v>70000</v>
@@ -1082,7 +1077,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="13">
         <v>0.22</v>
@@ -1090,147 +1085,147 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="C31" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="D31" s="18" t="s">
         <v>47</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="C32" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="D32" s="19" t="s">
         <v>51</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="C33" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="D33" s="19" t="s">
         <v>55</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="C34" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="D34" s="19" t="s">
         <v>59</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="C35" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="D35" s="19" t="s">
         <v>63</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="C36" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="D36" s="19" t="s">
         <v>67</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="C37" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="D37" s="19" t="s">
         <v>71</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="C38" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="19" t="s">
-        <v>75</v>
-      </c>
       <c r="D38" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="C42" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="D42" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="E42" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="21" t="s">
+      <c r="F42" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="F42" s="21" t="s">
+      <c r="G42" s="21" t="s">
         <v>82</v>
-      </c>
-      <c r="G42" s="21" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2795,28 +2790,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D1" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="E1" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="F1" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="G1" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="H1" s="25" t="s">
         <v>90</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3081,7 +3076,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3089,22 +3084,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4159,7 +4154,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -4167,16 +4162,16 @@
         <v>0</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="D39" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="E39" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>18</v>
@@ -5059,12 +5054,12 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B77" s="14">
         <f>E37</f>
@@ -5076,7 +5071,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B78" s="14">
         <f>F37</f>
@@ -5085,7 +5080,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B79" s="14">
         <f>F74</f>
@@ -5094,7 +5089,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B80" s="14">
         <f ca="1">IFERROR(_xlfn.SINGLE(_xlfn.MINIFS(A3:A37,A3:A37,"&gt;2000",G3:G37,"&gt;=0")),"-")</f>
@@ -5118,29 +5113,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="D3" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="E3" s="25" t="s">
         <v>107</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="17">
         <f>MAX(0,IF(Situation!$B$9="Married Filing Jointly",Situation!$D$45,IF(Situation!$B$9="Head of Household",Situation!$F$45,Situation!$B$45))+IF(Situation!$B$9="Married Filing Jointly",30000,IF(Situation!$B$9="Head of Household",22500,15000))-Situation!$B$10)</f>
@@ -5148,15 +5143,15 @@
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>110</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" s="17">
         <f>SUM(Situation!$B$19:$B$25)/Situation!$B$18</f>
@@ -5174,7 +5169,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="17">
         <f>MAX(0,IF(Situation!$B$9="Married Filing Jointly",Situation!$D$44,IF(Situation!$B$9="Head of Household",Situation!$F$44,Situation!$B$44))+IF(Situation!$B$9="Married Filing Jointly",30000,IF(Situation!$B$9="Head of Household",22500,15000))-Situation!$B$10)</f>
@@ -5182,15 +5177,15 @@
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -5203,7 +5198,7 @@
         <v>618355.99924464012</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
